--- a/education_forms/017_ai_generated_assignment_review_consent_form--education_forms.xlsx
+++ b/education_forms/017_ai_generated_assignment_review_consent_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -971,12 +971,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_i_consent',_'value':_true}</t>
+          <t>yes,_i_consent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, I consent', 'value': True}</t>
+          <t>Yes, I consent</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'no,_i_do_not_consent_(manual_review_only)',_'value':_false}</t>
+          <t>no,_i_do_not_consent_(manual_review_only)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'No, I do not consent (Manual review only)', 'value': False}</t>
+          <t>No, I do not consent (Manual review only)</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_"i_understand_that_my_data_will_be_processed_according_to_the_institution's_privacy_policy_and_will_not_be_used_to_train_external_ai_models.",_'value':_'acknowledged'}</t>
+          <t>i_understand_that_my_data_will_be_processed_according_to_the_institution's_privacy_policy_and_will_not_be_used_to_train_external_ai_models.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': "I understand that my data will be processed according to the institution's privacy policy and will not be used to train external AI models.", 'value': 'acknowledged'}</t>
+          <t>I understand that my data will be processed according to the institution's privacy policy and will not be used to train external AI models.</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'all_assignments_for_the_duration_of_this_course',_'value':_'all'}</t>
+          <t>all_assignments_for_the_duration_of_this_course</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'All assignments for the duration of this course', 'value': 'all'}</t>
+          <t>All assignments for the duration of this course</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'specific_assignments_only_(please_list_below)',_'value':_'specific'}</t>
+          <t>specific_assignments_only_(please_list_below)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Specific assignments only (Please list below)', 'value': 'specific'}</t>
+          <t>Specific assignments only (Please list below)</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'i_understand_that_ai_feedback_is_supplementary_and_all_final_academic_decisions_are_made_by_human_faculty.',_'value':_'understood'}</t>
+          <t>i_understand_that_ai_feedback_is_supplementary_and_all_final_academic_decisions_are_made_by_human_faculty.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'I understand that AI feedback is supplementary and all final academic decisions are made by human faculty.', 'value': 'understood'}</t>
+          <t>I understand that AI feedback is supplementary and all final academic decisions are made by human faculty.</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'i_agree_and_sign_this_consent_form',_'value':_'signed'}</t>
+          <t>i_agree_and_sign_this_consent_form</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'I agree and sign this consent form', 'value': 'signed'}</t>
+          <t>I agree and sign this consent form</t>
         </is>
       </c>
     </row>
